--- a/admin/ThePrimeFit_Sheets.xlsx
+++ b/admin/ThePrimeFit_Sheets.xlsx
@@ -22,7 +22,9 @@
     <sheet name="Salary" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Expenses" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Renewals" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Activity Log" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Doctors" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Content" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Activity Log" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +492,7 @@
   <dimension ref="A8:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="8">
@@ -503,7 +505,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>www.theprimefit.com · Transform today, thrive tomorrow</t>
+          <t>www.theprimefit.in · Transform today, thrive tomorrow</t>
         </is>
       </c>
     </row>
@@ -520,7 +522,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1. Upload this file to Google Drive, open it, then File → Save as Google Sheets.</t>
+          <t>1. Upload this file to Google Drive, open it, then File → Save as Google Sheets. (Or keep using your current sheet: just paste the new Code.gs into it.)</t>
         </is>
       </c>
     </row>
@@ -541,14 +543,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>4. Deploy → New deployment → Web app. Execute as: Me. Who has access: Anyone. Copy the web app URL.</t>
+          <t>4. Deploy → New deployment → Web app. Execute as: Me. Who has access: Anyone. Copy the web app URL. (After changing Code.gs: Deploy → Manage deployments → Edit → New version.)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>5. In The Prime Fit app: Clinic admin → Settings → Google Sheet. Paste the URL and the secret, then Save.</t>
+          <t>5. In The Prime Fit app: Settings → Google Sheet. Paste the URL and the secret, then Save. Use "Load from Google Sheet" or "Send this device's data" any time.</t>
         </is>
       </c>
     </row>
@@ -565,7 +567,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The app saves all data here. Each save rewrites the 15 sheets (Dashboard … Activity Log), so edit data in the app, not in the sheets.</t>
+          <t>The app saves all data here. Each save rewrites the 17 sheets (Dashboard … Activity Log, including Doctors and Content), so edit data in the app, not in the sheets.</t>
         </is>
       </c>
     </row>
@@ -604,7 +606,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
@@ -640,7 +642,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Used (injection kit)</t>
+          <t>Used (kit)</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -1479,13 +1481,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1501,10 +1505,20 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Payment Method</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1589,6 +1603,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Speciality</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00015B53"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Editing Cost</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00015B53"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1632,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2023,15 +2189,54 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Videos Edited</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Videos Posted</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Videos Remaining</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Updated</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-10-01T15:56:04.902Z</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-01T16:36:33.841Z</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2045,7 +2250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2056,10 +2261,11 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2090,35 +2296,40 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>Doctor</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Online Link</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>

--- a/admin/ThePrimeFit_Sheets.xlsx
+++ b/admin/ThePrimeFit_Sheets.xlsx
@@ -24,7 +24,8 @@
     <sheet name="Renewals" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Doctors" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Content" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Activity Log" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Editors" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Activity Log" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -193,6 +194,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -489,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A8:A21"/>
+  <dimension ref="A8:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -567,7 +571,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The app saves all data here. Each save rewrites the 17 sheets (Dashboard … Activity Log, including Doctors and Content), so edit data in the app, not in the sheets.</t>
+          <t>The app saves all data here. Each save rewrites the 18 sheets (Dashboard … Activity Log, including Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
         </is>
       </c>
     </row>
@@ -585,6 +589,14 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1481,7 +1493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1490,6 +1502,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1521,6 +1534,11 @@
       <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Note</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Counted</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1686,9 +1704,10 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1719,25 +1738,30 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>Scheduled</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Posted</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Editing Cost</t>
-        </is>
-      </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
+          <t>Editor Fee</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1749,6 +1773,67 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00015B53"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Fee per Video</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Videos Received</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Videos Posted</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Total Fees</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00015B53"/>
@@ -2233,7 +2318,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-01T16:36:33.841Z</t>
+          <t>2026-10-01T17:12:29.724Z</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>

--- a/admin/ThePrimeFit_Sheets.xlsx
+++ b/admin/ThePrimeFit_Sheets.xlsx
@@ -15,17 +15,18 @@
     <sheet name="Injection Sales" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Protein Sales" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Diet Support" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Purchases" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Inventory" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Team" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Incentives" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Salary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Expenses" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Renewals" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Doctors" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Content" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Editors" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Activity Log" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Service Sales" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Purchases" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Inventory" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Team" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Incentives" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Salary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Expenses" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Renewals" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Doctors" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Content" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Editors" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Activity Log" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -87,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -95,6 +96,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,12 +495,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A8:A29"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -571,7 +580,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The app saves all data here. Each save rewrites the 18 sheets (Dashboard … Activity Log, including Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
+          <t>The app saves all data here. Each save rewrites the 19 sheets (Dashboard … Activity Log, including Service Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
         </is>
       </c>
     </row>
@@ -589,14 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -606,679 +607,81 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Opening Stock</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Purchased Stock</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Sold Stock</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Used (kit)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Adjusted</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Available Stock</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Low Stock At</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Order Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Mounjaro 2.5mg</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Mounjaro 5mg</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Mounjaro 10mg</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ORDER REQUIRED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mounjaro 15mg</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ORDER REQUIRED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Wegovy 0.25mg</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Wegovy 1mg</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Wegovy 2.4mg</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ozempic 0.25mg</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ozempic 1mg</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Protein</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Protein Sachets</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>20</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ORDER REQUIRED</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Needles</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Needles</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Alcohol Swabs</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Alcohol Swabs</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>20</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Insulin Syringes</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Insulin Syringes</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>20</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ice Gel Packs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ice Gel Packs</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Travel Bags</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Travel Bags</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>20</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Invoice No</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Invoice Product Name</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Expiry</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>GST %</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Line Total</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1288,74 +691,820 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Designation</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Salary</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Incentive Status</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Injection Incentive</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Protein Incentive</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Pay Counts</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Joining Date</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Opening Stock</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Purchased Stock</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Sold Stock</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Used (kit)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Adjusted</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Available Stock</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Low Stock At</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Order Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mounjaro 2.5mg</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mounjaro 5mg</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mounjaro 10mg</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ORDER REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mounjaro 15mg</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ORDER REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Wegovy 0.25mg</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wegovy 1mg</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wegovy 2.4mg</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ozempic 0.25mg</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ozempic 1mg</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Protein</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Protein Sachets</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ORDER REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GLP-1 Success Support</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GLP-1 Success Support · 1 Week</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GLP-1 Success Support</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GLP-1 Success Support · 1 Month</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GLP-1 Success Support</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GLP-1 Success Support · 2 Months</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GLP-1 Success Support</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GLP-1 Success Support · 3 Months</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Needles</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Needles</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alcohol Swabs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alcohol Swabs</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Insulin Syringes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Insulin Syringes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ice Gel Packs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ice Gel Packs</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Travel Bags</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Travel Bags</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1516,84 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Designation</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Incentive Status</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Injection Incentive</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Protein Incentive</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Pay Counts</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Joining Date</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1375,7 +1601,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1384,37 +1610,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Team Member</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Sale Type</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Incentive</t>
         </is>
@@ -1425,10 +1651,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1437,45 +1662,45 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Designation</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Incentive</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Total Pay</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Booked as Expense</t>
         </is>
@@ -1486,10 +1711,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1500,43 +1724,43 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Counted</t>
         </is>
@@ -1547,10 +1771,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1560,125 +1783,52 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Last Purchase Date</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Days Since</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Reminder</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Reference Team</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Contacted</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00015B53"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Speciality</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Days</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Appointments</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1840,78 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Speciality</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1705,63 +1926,63 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Editor</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Posted</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Editor Fee</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1772,10 +1993,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1784,90 +2004,47 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Fee per Video</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Videos Received</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Videos Posted</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Total Fees</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00015B53"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Date &amp; Time</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>By</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Details</t>
         </is>
       </c>
     </row>
@@ -1879,30 +2056,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>This month</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>All time</t>
         </is>
@@ -2101,7 +2277,6 @@
           <t>Mounjaro 10mg (0), Mounjaro 15mg (0), Protein Sachets (0)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2200,8 +2375,6 @@
           <t>Top Performer</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2212,7 +2385,6 @@
       <c r="B25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2223,7 +2395,6 @@
       <c r="B26" t="n">
         <v>0</v>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2234,7 +2405,6 @@
       <c r="B27" t="n">
         <v>0</v>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2245,7 +2415,6 @@
       <c r="B28" t="n">
         <v>0</v>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2256,7 +2425,6 @@
       <c r="B29" t="n">
         <v>0</v>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2269,7 +2437,6 @@
           <t>Mounjaro 2.5mg (0), Mounjaro 5mg (0), Mounjaro 10mg (0), Mounjaro 15mg (0), Wegovy 0.25mg (0), Wegovy 1mg (0), Wegovy 2.4mg (0), Ozempic 0.25mg (0), Ozempic 1mg (0), Protein Sachets (0), Needles (0), Alcohol Swabs (0), Insulin Syringes (0), Ice Gel Packs (0), Travel Bags (0)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2318,10 +2485,51 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-01T17:12:29.724Z</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>2026-10-01T17:49:06.989Z</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Date &amp; Time</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>By</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2331,7 +2539,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2347,74 +2554,74 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Doctor</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Online Link</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2428,11 +2635,214 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Alt Mobile</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Interested In</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Next Follow-up</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>Target (kg)</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>Height (cm)</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>Last Note</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>Added By</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>First Purchase</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Last Purchase</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Total Spent</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Last Product</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Reference Team</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2443,113 +2853,77 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Alt Mobile</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Interested In</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Assigned To</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>Next Follow-up</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>Weight (kg)</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>Target (kg)</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>Height (cm)</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>Last Note</t>
-        </is>
-      </c>
-      <c r="S1" s="4" t="inlineStr">
-        <is>
-          <t>Added By</t>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>New/Renewal</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Shared Reference</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Dietitian</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Incentive</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -2558,87 +2932,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>First Purchase</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Last Purchase</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Orders</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Total Spent</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Last Product</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Reference Team</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00015B53"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2648,161 +2948,64 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>New/Renewal</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Shared Reference</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Dietitian</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Incentive</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00015B53"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Protein Type</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Shared Reference</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Split</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Incentive</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2816,7 +3019,6 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2829,59 +3031,59 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Shared Reference</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Split</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Incentive</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2895,80 +3097,85 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00015B53"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Invoice No</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Invoice Product Name</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>New/Renewal</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Service / Package</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Expiry</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>GST %</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Line Total</t>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Shared Reference</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Incentive</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>

--- a/admin/ThePrimeFit_Sheets.xlsx
+++ b/admin/ThePrimeFit_Sheets.xlsx
@@ -15,18 +15,19 @@
     <sheet name="Injection Sales" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Protein Sales" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Diet Support" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Service Sales" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Purchases" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Inventory" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Team" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Incentives" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Salary" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Expenses" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Renewals" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Doctors" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Content" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Editors" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Activity Log" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Other Sales" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Service Sales" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Purchases" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Inventory" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Team" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Incentives" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Salary" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Expenses" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Renewals" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Doctors" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Content" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Editors" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Activity Log" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -580,7 +581,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The app saves all data here. Each save rewrites the 19 sheets (Dashboard … Activity Log, including Service Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
+          <t>The app saves all data here. Each save rewrites the 20 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
         </is>
       </c>
     </row>
@@ -605,6 +606,96 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>New/Renewal</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Service / Package</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Shared Reference</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Incentive</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -688,13 +779,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -770,16 +861,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>GLP-1 Success Support</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mounjaro 2.5mg</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
+          <t>GLP-1 Success Support · 1 Week</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -793,31 +886,34 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>GLP-1 Success Support</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mounjaro 5mg</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
+          <t>GLP-1 Success Support · 1 Month</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -831,31 +927,34 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>GLP-1 Success Support</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mounjaro 10mg</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+          <t>GLP-1 Success Support · 2 Months</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -869,36 +968,34 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ORDER REQUIRED</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>GLP-1 Success Support</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mounjaro 15mg</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
+          <t>GLP-1 Success Support · 3 Months</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -912,608 +1009,25 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ORDER REQUIRED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Wegovy 0.25mg</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Wegovy 1mg</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Wegovy 2.4mg</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ozempic 0.25mg</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Injection</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ozempic 1mg</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Protein</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Protein Sachets</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>20</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ORDER REQUIRED</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GLP-1 Success Support</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GLP-1 Success Support · 1 Week</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
           <t>Service</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GLP-1 Success Support</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GLP-1 Success Support · 1 Month</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>GLP-1 Success Support</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GLP-1 Success Support · 2 Months</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GLP-1 Success Support</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>GLP-1 Success Support · 3 Months</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Unlimited</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Needles</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Needles</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>20</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alcohol Swabs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Alcohol Swabs</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>20</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Insulin Syringes</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Insulin Syringes</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ice Gel Packs</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ice Gel Packs</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>20</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Travel Bags</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Travel Bags</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1591,7 +1105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1651,7 +1165,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1711,7 +1225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1771,7 +1285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1837,7 +1351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1909,7 +1423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1993,7 +1507,438 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>This month</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>All time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Injection Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Protein Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Diet Support Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Consultation Fees</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Clinic Visits</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Online Consultations</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>New Leads</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Leads Converted</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Open Leads</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Order Required</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total Patients</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>New Patients</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Renewal Patients</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Active Patients</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Team Members</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Incentives</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Monthly Salary</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Top Performer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Injection Stock</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Protein Stock</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Needles Stock</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Swabs Stock</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Syringe Stock</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Low Stock Alerts</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Videos Edited</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Videos Posted</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Videos Remaining</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-01T18:34:37.012Z</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2053,448 +1998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>This month</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>All time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Total Orders</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Net Profit</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Injection Sales</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Protein Sales</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Diet Support Sales</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Consultation Fees</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Appointments</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Clinic Visits</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Online Consultations</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>New Leads</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Leads Converted</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Open Leads</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Order Required</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Mounjaro 10mg (0), Mounjaro 15mg (0), Protein Sachets (0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total Patients</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>New Patients</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Renewal Patients</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Active Patients</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Team Members</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Total Incentives</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Monthly Salary</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Top Performer</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Injection Stock</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Protein Stock</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Needles Stock</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Swabs Stock</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Syringe Stock</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Low Stock Alerts</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mounjaro 2.5mg (0), Mounjaro 5mg (0), Mounjaro 10mg (0), Mounjaro 15mg (0), Wegovy 0.25mg (0), Wegovy 1mg (0), Wegovy 2.4mg (0), Ozempic 0.25mg (0), Ozempic 1mg (0), Protein Sachets (0), Needles (0), Alcohol Swabs (0), Insulin Syringes (0), Ice Gel Packs (0), Travel Bags (0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Videos Edited</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Videos Posted</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Videos Remaining</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Updated</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-10-01T17:49:06.989Z</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2542,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2554,10 +2058,11 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2588,40 +2093,45 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>Clinic</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>Doctor</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Online Link</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3100,21 +2610,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3125,55 +2636,60 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>New/Renewal</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Service / Package</t>
-        </is>
-      </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Shared Reference</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Split</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Incentive</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>

--- a/admin/ThePrimeFit_Sheets.xlsx
+++ b/admin/ThePrimeFit_Sheets.xlsx
@@ -27,7 +27,10 @@
     <sheet name="Doctors" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Content" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Editors" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Activity Log" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Campaigns" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Tasks" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Attendance" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Activity Log" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -581,7 +584,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The app saves all data here. Each save rewrites the 20 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
+          <t>The app saves all data here. Each save rewrites the 23 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1931,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-01T18:34:37.012Z</t>
+          <t>2026-10-01T19:17:21.198Z</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1999,6 +2002,204 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Campaign</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Spent</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Converted</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Cost per Lead</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Done By</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Team Member</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/admin/ThePrimeFit_Sheets.xlsx
+++ b/admin/ThePrimeFit_Sheets.xlsx
@@ -28,9 +28,11 @@
     <sheet name="Content" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Editors" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Campaigns" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Tasks" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Attendance" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Activity Log" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Ads Report" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Tasks" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Attendance" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Founder Notes" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Activity Log" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,7 +586,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The app saves all data here. Each save rewrites the 23 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
+          <t>The app saves all data here. Each save rewrites the 25 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
         </is>
       </c>
     </row>
@@ -1234,16 +1236,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1254,32 +1258,42 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Counted</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Ad Leads (manual)</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1945,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-01T19:17:21.198Z</t>
+          <t>2026-10-01T20:05:54.070Z</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -2107,6 +2121,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Ad Spend</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Leads (app)</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Leads (manual)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Cost per Lead</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Converted</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2163,7 +2243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2199,7 +2279,73 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Pinned</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>By</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/admin/ThePrimeFit_Sheets.xlsx
+++ b/admin/ThePrimeFit_Sheets.xlsx
@@ -31,8 +31,9 @@
     <sheet name="Ads Report" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Tasks" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="Attendance" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Founder Notes" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Activity Log" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Founders" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Founder Notes" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Activity Log" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -586,7 +587,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The app saves all data here. Each save rewrites the 25 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
+          <t>The app saves all data here. Each save rewrites the 26 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1244,10 +1245,11 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1263,35 +1265,40 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Counted</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Ad Leads (manual)</t>
         </is>
@@ -1945,7 +1952,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-01T20:05:54.070Z</t>
+          <t>2026-10-01T20:37:27.726Z</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -2285,7 +2292,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Profit Share %</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Monthly Limit</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Spent (all time)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Spent this month</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Invested</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Net Capital</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Capital entries</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2296,6 +2414,12 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2306,35 +2430,65 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>With</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Minutes</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Outcome / Decision</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Next Step</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Due</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Pinned</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>By</t>
         </is>
@@ -2345,7 +2499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/admin/ThePrimeFit_Sheets.xlsx
+++ b/admin/ThePrimeFit_Sheets.xlsx
@@ -33,7 +33,8 @@
     <sheet name="Attendance" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="Founders" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="Founder Notes" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Activity Log" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Slips" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Activity Log" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -587,7 +588,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The app saves all data here. Each save rewrites the 26 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors and Content), so edit data in the app, not in the sheets.</t>
+          <t>The app saves all data here. Each save rewrites the 27 sheets (Dashboard … Activity Log, including Service Sales, Other Sales, Doctors, Editors, Content and Slips), so edit data in the app, not in the sheets.</t>
         </is>
       </c>
     </row>
@@ -897,13 +898,11 @@
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -938,13 +937,11 @@
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -979,13 +976,11 @@
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1020,13 +1015,11 @@
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1738,8 +1731,6 @@
           <t>Order Required</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1838,8 +1829,6 @@
           <t>Top Performer</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1850,7 +1839,6 @@
       <c r="B25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1861,7 +1849,6 @@
       <c r="B26" t="n">
         <v>0</v>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1872,7 +1859,6 @@
       <c r="B27" t="n">
         <v>0</v>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1883,7 +1869,6 @@
       <c r="B28" t="n">
         <v>0</v>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1894,7 +1879,6 @@
       <c r="B29" t="n">
         <v>0</v>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1902,8 +1886,6 @@
           <t>Low Stock Alerts</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1955,7 +1937,6 @@
           <t>2026-10-01T20:37:27.726Z</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2500,6 +2481,90 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Slip No.</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Made By</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Made On</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Sale Invoice Nos.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
